--- a/Calc_Width_Lifetime.xlsx
+++ b/Calc_Width_Lifetime.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Si24\root_scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{483A74E2-4D99-4AE8-AB2F-7234F7D398BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D197EFE-C280-41F4-95D9-B07525493F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{54B87DC3-80D2-408F-9ECA-DC6AAEA4FCE2}"/>
+    <workbookView xWindow="348" yWindow="504" windowWidth="12564" windowHeight="12000" xr2:uid="{54B87DC3-80D2-408F-9ECA-DC6AAEA4FCE2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
   <si>
     <t>τ (fs)</t>
   </si>
@@ -112,11 +112,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0E+00"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,6 +185,13 @@
       <name val="Cambria"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -220,7 +228,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -252,13 +260,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2027,7 +2038,7 @@
         <v>13</v>
       </c>
       <c r="B6" s="6">
-        <v>5.0000000000000001E-3</v>
+        <v>5.8</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -2050,7 +2061,7 @@
       </c>
       <c r="B7" s="3">
         <f>B6/$B$2</f>
-        <v>5.0000000000000001E-9</v>
+        <v>5.7999999999999995E-6</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>8</v>
@@ -2073,7 +2084,7 @@
       </c>
       <c r="B8" s="2">
         <f>B4/$B$6</f>
-        <v>1.3164239138000002E-13</v>
+        <v>1.1348482015517243E-16</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
@@ -2096,7 +2107,7 @@
       </c>
       <c r="B9" s="9">
         <f>B8*$B$3</f>
-        <v>131.64239138000002</v>
+        <v>0.11348482015517243</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>9</v>
@@ -2119,7 +2130,7 @@
       </c>
       <c r="B10" s="8">
         <f>B9*LN(2)</f>
-        <v>91.247552427215865</v>
+        <v>7.8661683126910228E-2</v>
       </c>
       <c r="C10" s="1" t="str">
         <f>C9</f>
@@ -2167,14 +2178,14 @@
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="13">
-        <v>1.1200000000000001</v>
+      <c r="B13" s="14">
+        <v>104000000</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="12">
-        <v>0.18</v>
+      <c r="D13" s="13">
+        <v>3</v>
       </c>
       <c r="F13" s="4">
         <v>1.1000000000000001</v>
@@ -2194,7 +2205,7 @@
       </c>
       <c r="B14" s="2">
         <f>B13/$B$3</f>
-        <v>1.1200000000000001E-15</v>
+        <v>1.04E-7</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
@@ -2217,7 +2228,7 @@
       </c>
       <c r="B15" s="7">
         <f>$B$4/B14</f>
-        <v>0.58768924723214289</v>
+        <v>6.3289611240384617E-9</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -2240,7 +2251,7 @@
       </c>
       <c r="B16" s="2">
         <f>B15/$B$2</f>
-        <v>5.8768924723214289E-7</v>
+        <v>6.3289611240384614E-15</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>8</v>
@@ -2263,7 +2274,7 @@
       </c>
       <c r="B17" s="11">
         <f>B13*LN(2)</f>
-        <v>0.77632484222713882</v>
+        <v>72087306.778234303</v>
       </c>
       <c r="C17" s="1" t="str">
         <f>C13</f>
@@ -2271,7 +2282,7 @@
       </c>
       <c r="D17" s="11">
         <f>D13*LN(2)</f>
-        <v>0.12476649250079015</v>
+        <v>2.0794415416798357</v>
       </c>
       <c r="F17" s="4">
         <v>1.5</v>
@@ -2324,7 +2335,16 @@
         <v>0.25346542340893291</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" ht="18.600000000000001">
+      <c r="A21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="10">
+        <v>31.4</v>
+      </c>
+      <c r="D21" s="10">
+        <v>4</v>
+      </c>
       <c r="F21" s="4">
         <v>1.9</v>
       </c>
@@ -2338,6 +2358,17 @@
       </c>
     </row>
     <row r="22" spans="1:8">
+      <c r="A22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="12">
+        <f>B21/LN(2)</f>
+        <v>45.30062428391345</v>
+      </c>
+      <c r="D22" s="12">
+        <f>D21/LN(2)</f>
+        <v>5.7707801635558535</v>
+      </c>
       <c r="F22" s="4">
         <v>2</v>
       </c>

--- a/Calc_Width_Lifetime.xlsx
+++ b/Calc_Width_Lifetime.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Si24\root_scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D197EFE-C280-41F4-95D9-B07525493F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CDB9BDD-1F31-41B5-8F82-72B404BBE09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="348" yWindow="504" windowWidth="12564" windowHeight="12000" xr2:uid="{54B87DC3-80D2-408F-9ECA-DC6AAEA4FCE2}"/>
+    <workbookView xWindow="5760" yWindow="0" windowWidth="17280" windowHeight="9072" xr2:uid="{54B87DC3-80D2-408F-9ECA-DC6AAEA4FCE2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -248,9 +248,6 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -270,6 +267,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="11" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1949,7 +1949,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="1"/>
     <col min="5" max="5" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -1958,7 +1958,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="8">
         <f>B8*$B$3</f>
         <v>0.11348482015517243</v>
       </c>
@@ -2128,7 +2128,7 @@
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="7">
         <f>B9*LN(2)</f>
         <v>7.8661683126910228E-2</v>
       </c>
@@ -2178,14 +2178,14 @@
       <c r="A13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="14">
-        <v>104000000</v>
+      <c r="B13" s="13">
+        <v>97920000</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="13">
-        <v>3</v>
+      <c r="D13" s="12">
+        <v>10</v>
       </c>
       <c r="F13" s="4">
         <v>1.1000000000000001</v>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="B14" s="2">
         <f>B13/$B$3</f>
-        <v>1.04E-7</v>
+        <v>9.7920000000000006E-8</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
@@ -2226,9 +2226,9 @@
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="14">
         <f>$B$4/B14</f>
-        <v>6.3289611240384617E-9</v>
+        <v>6.7219358343545752E-9</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B16" s="2">
         <f>B15/$B$2</f>
-        <v>6.3289611240384614E-15</v>
+        <v>6.721935834354575E-15</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>8</v>
@@ -2272,17 +2272,17 @@
       <c r="A17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="10">
         <f>B13*LN(2)</f>
-        <v>72087306.778234303</v>
+        <v>67872971.920429841</v>
       </c>
       <c r="C17" s="1" t="str">
         <f>C13</f>
         <v>fs</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="10">
         <f>D13*LN(2)</f>
-        <v>2.0794415416798357</v>
+        <v>6.9314718055994531</v>
       </c>
       <c r="F17" s="4">
         <v>1.5</v>
@@ -2339,10 +2339,10 @@
       <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="9">
         <v>31.4</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="9">
         <v>4</v>
       </c>
       <c r="F21" s="4">
@@ -2361,11 +2361,11 @@
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="11">
         <f>B21/LN(2)</f>
         <v>45.30062428391345</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="11">
         <f>D21/LN(2)</f>
         <v>5.7707801635558535</v>
       </c>
